--- a/outputs/daily/hr_rankings_2026-10-26.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-26.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>55.7</v>
+        <v>57.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.7</v>
+        <v>54.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1084,7 +1088,7 @@
         <v>33.4</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
         <v>92.09999999999999</v>
@@ -1272,8 +1276,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1287,24 +1299,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -1312,31 +1324,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1354,22 +1366,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1383,7 +1395,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1425,12 +1437,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1440,12 +1452,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1455,101 +1467,109 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1563,24 +1583,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -1588,31 +1608,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.8</v>
+        <v>50.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,62 +1646,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>50.1</v>
+        <v>43.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1701,27 +1717,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1731,101 +1747,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1864,7 +1888,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1912,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.1</v>
+        <v>49.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1912,7 +1936,7 @@
         <v>33.4</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
         <v>95.5</v>
@@ -2100,8 +2124,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2120,7 +2152,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2140,7 +2172,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2196,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>49.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2210,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2220,10 @@
         <v>38.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -2201,39 +2233,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2404,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2391,24 +2427,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -2416,31 +2452,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.4</v>
+        <v>48.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,26 +2490,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2487,7 +2523,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2529,12 +2565,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2544,72 +2580,72 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2619,41 +2655,49 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2667,12 +2711,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,12 +2736,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2716,7 +2760,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>46.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,26 +2774,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
         <v>33.4</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>13.3</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2763,7 +2807,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2805,7 +2849,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -2815,87 +2859,87 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2928,8 +2972,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2943,24 +2995,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -2968,31 +3020,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.2</v>
+        <v>45.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,62 +3058,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>43.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>54.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3081,12 +3129,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3096,12 +3144,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,101 +3159,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3244,7 +3300,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3324,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.3</v>
+        <v>45.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3292,7 +3348,7 @@
         <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
         <v>71.7</v>
@@ -3480,8 +3536,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3520,12 +3584,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3608,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3622,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3632,10 @@
         <v>38.7</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -3581,39 +3645,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3756,8 +3816,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3771,12 +3839,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3864,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3888,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.9</v>
+        <v>38.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3902,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q13" t="n">
         <v>38.7</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3914,7 +3978,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3924,7 +3988,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -3939,67 +4003,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4096,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4072,12 +4144,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4168,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4182,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4192,10 @@
         <v>38.7</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -4133,39 +4205,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4308,8 +4376,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4323,24 +4399,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -4348,31 +4424,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.9</v>
+        <v>34.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,65 +4462,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>5.1</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4461,12 +4533,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4548,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,101 +4563,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4599,12 +4679,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,12 +4704,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4728,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>32.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4666,22 +4746,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>31.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>5.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4695,7 +4775,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4720,7 +4800,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,12 +4817,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4832,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,67 +4847,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4860,8 +4940,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4875,12 +4963,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4900,12 +4988,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +5012,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.7</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,26 +5026,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4971,7 +5059,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4996,7 +5084,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5013,12 +5101,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5116,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,67 +5131,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5136,8 +5224,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5151,24 +5247,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -5176,31 +5272,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.8</v>
+        <v>31.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5218,22 +5314,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>10.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>24.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5247,7 +5343,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5272,7 +5368,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5294,7 +5390,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,12 +5400,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,101 +5415,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5452,7 +5556,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5580,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.7</v>
+        <v>31.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5594,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5604,10 @@
         <v>37.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5513,39 +5617,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5688,8 +5788,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6054,12 +6162,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6186,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>55.7</v>
+        <v>57.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6200,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6210,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -6115,39 +6223,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6394,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6330,7 +6442,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6466,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.7</v>
+        <v>54.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6378,7 +6490,7 @@
         <v>33.4</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
         <v>92.09999999999999</v>
@@ -6566,8 +6678,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6581,24 +6701,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -6606,31 +6726,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6648,22 +6768,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -6677,7 +6797,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -6719,12 +6839,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6734,12 +6854,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6749,101 +6869,109 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6857,24 +6985,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -6882,31 +7010,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.8</v>
+        <v>50.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,62 +7048,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>50.1</v>
+        <v>43.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6995,27 +7119,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7025,101 +7149,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7158,7 +7290,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7314,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.1</v>
+        <v>49.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7206,7 +7338,7 @@
         <v>33.4</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
         <v>95.5</v>
@@ -7394,8 +7526,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7414,7 +7554,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7434,7 +7574,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7598,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.4</v>
+        <v>49.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7612,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7622,10 @@
         <v>38.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -7495,39 +7635,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7806,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7685,24 +7829,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7710,31 +7854,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.4</v>
+        <v>48.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,26 +7892,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7781,7 +7925,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7823,12 +7967,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7838,72 +7982,72 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -7913,41 +8057,49 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7961,12 +8113,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,12 +8138,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8010,7 +8162,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>46.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,26 +8176,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
         <v>33.4</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>13.3</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8057,7 +8209,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8099,7 +8251,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -8109,87 +8261,87 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8222,8 +8374,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8237,24 +8397,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8262,31 +8422,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.2</v>
+        <v>45.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,62 +8460,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>43.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>54.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8375,12 +8531,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8390,12 +8546,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,101 +8561,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8538,7 +8702,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8726,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.3</v>
+        <v>45.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8586,7 +8750,7 @@
         <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
         <v>71.7</v>
@@ -8774,8 +8938,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8814,12 +8986,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +9010,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +9024,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +9034,10 @@
         <v>38.7</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>78</v>
@@ -8875,39 +9047,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9050,8 +9218,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9065,12 +9241,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9266,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9290,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.9</v>
+        <v>38.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9304,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q13" t="n">
         <v>38.7</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9208,7 +9380,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -9218,7 +9390,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -9233,67 +9405,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9498,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9366,12 +9546,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9570,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9584,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9594,10 @@
         <v>38.7</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -9427,39 +9607,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9602,8 +9778,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9617,24 +9801,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -9642,31 +9826,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.9</v>
+        <v>34.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,65 +9864,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>5.1</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9755,12 +9935,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9950,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,101 +9965,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9893,12 +10081,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,12 +10106,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +10130,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>32.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9960,22 +10148,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>31.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>5.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9989,7 +10177,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -10014,7 +10202,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,12 +10219,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10234,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,67 +10249,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10154,8 +10342,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10169,12 +10365,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10194,12 +10390,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10414,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.7</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,26 +10428,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -10265,7 +10461,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -10290,7 +10486,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10307,12 +10503,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10518,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,67 +10533,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10430,8 +10626,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10445,24 +10649,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -10470,31 +10674,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.8</v>
+        <v>31.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10512,22 +10716,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>10.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>24.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -10541,7 +10745,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -10566,7 +10770,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10588,7 +10792,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,12 +10802,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,101 +10817,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10746,7 +10958,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10982,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.7</v>
+        <v>31.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10996,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +11006,10 @@
         <v>37.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10807,39 +11019,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10982,8 +11190,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>

--- a/outputs/daily/hr_rankings_2026-10-26.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-26.xlsx
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>54.6</v>
+        <v>55.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1091,7 +1091,7 @@
         <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1101,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1348,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1362,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1375,7 +1371,7 @@
         <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1385,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1863,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -1893,22 +1885,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1926,62 +1918,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R6" t="n">
         <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2001,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2031,97 +2019,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -2147,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -2177,26 +2165,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49.9</v>
+        <v>48.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2210,26 +2198,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
         <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2243,7 +2231,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2281,27 +2269,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2311,97 +2299,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2427,12 +2415,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2457,7 +2445,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2476,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2490,11 +2478,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
         <v>33.4</v>
@@ -2503,49 +2491,45 @@
         <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2565,7 +2549,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -2575,12 +2559,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2590,72 +2574,72 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2711,12 +2695,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2741,7 +2725,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2760,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>46.1</v>
+        <v>48.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2774,11 +2758,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
         <v>33.4</v>
@@ -2787,49 +2771,45 @@
         <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2849,7 +2829,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -2859,87 +2839,87 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2995,24 +2975,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr.</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -3025,26 +3005,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.9</v>
+        <v>46.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3058,26 +3038,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43.6</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R10" t="n">
         <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>54.9</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3091,7 +3071,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3129,12 +3109,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3144,12 +3124,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3159,97 +3139,97 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -3275,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -3305,26 +3285,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>45.2</v>
+        <v>45.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3338,62 +3318,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R11" t="n">
         <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3413,12 +3389,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3428,12 +3404,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3443,97 +3419,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -4679,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4709,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4728,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4742,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R16" t="n">
         <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>23.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4817,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4832,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4847,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4963,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4993,7 +4965,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5012,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5026,11 +4998,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
@@ -5039,52 +5011,48 @@
         <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5101,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5116,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5131,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5247,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5277,7 +5245,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5296,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5310,11 +5278,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q18" t="n">
         <v>33.4</v>
@@ -5323,52 +5291,48 @@
         <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>17.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5385,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5400,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5415,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -6447,7 +6411,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6466,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>54.6</v>
+        <v>55.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6480,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6493,7 +6457,7 @@
         <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6503,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6750,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6764,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6777,7 +6737,7 @@
         <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6787,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7265,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7295,22 +7251,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -7328,62 +7284,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R6" t="n">
         <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7403,27 +7355,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7433,97 +7385,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -7549,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -7579,26 +7531,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49.9</v>
+        <v>48.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7612,26 +7564,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
         <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7645,7 +7597,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7683,27 +7635,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7713,97 +7665,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -7829,12 +7781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7859,7 +7811,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7878,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7892,11 +7844,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
         <v>33.4</v>
@@ -7905,49 +7857,45 @@
         <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7967,7 +7915,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -7977,12 +7925,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7992,72 +7940,72 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -8113,12 +8061,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8143,7 +8091,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8162,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>46.1</v>
+        <v>48.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8176,11 +8124,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
         <v>33.4</v>
@@ -8189,49 +8137,45 @@
         <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8251,7 +8195,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -8261,87 +8205,87 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8397,24 +8341,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr.</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8427,26 +8371,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.9</v>
+        <v>46.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8460,26 +8404,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43.6</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>38.7</v>
+        <v>33.4</v>
       </c>
       <c r="R10" t="n">
         <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>54.9</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8493,7 +8437,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8531,12 +8475,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8546,12 +8490,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8561,97 +8505,97 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -8677,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-27T00:00:00Z</t>
@@ -8707,26 +8651,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>45.2</v>
+        <v>45.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8740,62 +8684,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.4</v>
+        <v>38.7</v>
       </c>
       <c r="R11" t="n">
         <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8815,12 +8755,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -8830,12 +8770,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8845,97 +8785,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -10081,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10111,7 +10051,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10130,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10144,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R16" t="n">
         <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>23.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10219,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10234,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10249,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10365,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10395,7 +10331,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10414,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10428,11 +10364,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
@@ -10441,52 +10377,48 @@
         <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10503,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10518,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10533,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10649,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10679,7 +10611,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10698,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10712,11 +10644,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q18" t="n">
         <v>33.4</v>
@@ -10725,52 +10657,48 @@
         <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>17.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10787,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10802,12 +10730,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10817,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
